--- a/data/trans_orig/IP07_C11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C11_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener problemas para dormir en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de tener problemas para dormir, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3561</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8425</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4109</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10289</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>6,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8505</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9210</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1674</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10752</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2231</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6272</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3829</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5569</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17142</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11013</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24600</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10741</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6542</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16335</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17061</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>28511</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72383</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64816</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79891</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52205</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46124</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>57465</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>73259</t>
+          <t>54923</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64596</t>
+          <t>48084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80102</t>
+          <t>60592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>125464</t>
+          <t>127306</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114630</t>
+          <t>117204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134399</t>
+          <t>137963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5658</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1475</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11595</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2281</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3421</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7816</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3659</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8783</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27072</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18355</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41730</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41364</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15702</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>86935</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26531</t>
+          <t>18131</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40916</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67895</t>
+          <t>45203</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40725</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129892</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>138013</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124290</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>148430</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>86,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>89540</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48113</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>113321</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>139927</t>
+          <t>94547</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124777</t>
+          <t>83585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149084</t>
+          <t>102981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>229467</t>
+          <t>232560</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171004</t>
+          <t>216650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256332</t>
+          <t>247040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>363</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9456</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11524</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14624</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3897</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8931</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5576</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2519</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12080</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>44215</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>33013</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>60148</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>52104</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>26081</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>109831</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>52,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31683</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57711</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>73714</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68156</t>
+          <t>58318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>165121</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>210396</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>193599</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>223193</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>71,68%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>82,63%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>141745</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>92958</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>167316</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>67,35%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>79,5%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>213186</t>
+          <t>149470</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197874</t>
+          <t>138189</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226249</t>
+          <t>160236</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>354931</t>
+          <t>359867</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>292251</t>
+          <t>338542</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>382548</t>
+          <t>377405</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>577</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
